--- a/Excel/StockQuotation (6).xlsx
+++ b/Excel/StockQuotation (6).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:46</v>
+        <v>07/02/23 23:30:28</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>9256.95</v>
+        <v>9223.52</v>
       </c>
       <c r="B7" t="str">
-        <v>20.88 (0.226%)</v>
+        <v>11.67 (0.1266%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>9276.5</v>
+        <v>9241.96</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>9200.54</v>
+        <v>9197.46</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>51998643</v>
+        <v>103442462</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>788905989.95</v>
+        <v>1067576195.09</v>
       </c>
     </row>
     <row r="9">
@@ -534,19 +534,19 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="F11">
         <v>0.42</v>
       </c>
       <c r="G11">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="H11">
         <v>0.42</v>
@@ -558,22 +558,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>135500</v>
+        <v>33085588</v>
       </c>
       <c r="L11">
-        <v>57.081</v>
+        <v>14771.11967</v>
       </c>
       <c r="M11">
-        <v>1335100</v>
+        <v>500500</v>
       </c>
       <c r="N11">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="O11">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="P11">
-        <v>3283500</v>
+        <v>2836700</v>
       </c>
     </row>
     <row r="12">
@@ -587,13 +587,13 @@
         <v>2.06</v>
       </c>
       <c r="D12">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.9615384615384616</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G12">
         <v>2.08</v>
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1333100</v>
+        <v>1119925</v>
       </c>
       <c r="L12">
-        <v>2752.844</v>
+        <v>2299.92356</v>
       </c>
       <c r="M12">
-        <v>218100</v>
+        <v>1005000</v>
       </c>
       <c r="N12">
+        <v>2.04</v>
+      </c>
+      <c r="O12">
         <v>2.06</v>
       </c>
-      <c r="O12">
-        <v>2.08</v>
-      </c>
       <c r="P12">
-        <v>410700</v>
+        <v>200400</v>
       </c>
     </row>
     <row r="13">
@@ -634,46 +634,46 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="D13">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.6993006993006993</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G13">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H13">
+        <v>2.82</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>5323644</v>
+      </c>
+      <c r="L13">
+        <v>15143.35806</v>
+      </c>
+      <c r="M13">
+        <v>304700</v>
+      </c>
+      <c r="N13">
         <v>2.84</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>2930101</v>
-      </c>
-      <c r="L13">
-        <v>8392.54888</v>
-      </c>
-      <c r="M13">
-        <v>1038100</v>
-      </c>
-      <c r="N13">
+      <c r="O13">
         <v>2.86</v>
       </c>
-      <c r="O13">
-        <v>2.88</v>
-      </c>
       <c r="P13">
-        <v>1759300</v>
+        <v>1063800</v>
       </c>
     </row>
     <row r="14">
@@ -687,16 +687,16 @@
         <v>0.44</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2.3255813953488373</v>
       </c>
       <c r="F14">
         <v>0.44</v>
       </c>
       <c r="G14">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="H14">
         <v>0.43</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>13035501</v>
+        <v>10327040</v>
       </c>
       <c r="L14">
-        <v>5804.6824400000005</v>
+        <v>4537.1922</v>
       </c>
       <c r="M14">
-        <v>642000</v>
+        <v>457500</v>
       </c>
       <c r="N14">
         <v>0.44</v>
@@ -723,7 +723,7 @@
         <v>0.45</v>
       </c>
       <c r="P14">
-        <v>2595000</v>
+        <v>1798100</v>
       </c>
     </row>
     <row r="15">
@@ -734,46 +734,46 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="D15">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>0.6024096385542169</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F15">
+        <v>8.25</v>
+      </c>
+      <c r="G15">
         <v>8.3</v>
       </c>
-      <c r="G15">
-        <v>8.35</v>
-      </c>
       <c r="H15">
+        <v>8.25</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>137355</v>
+      </c>
+      <c r="L15">
+        <v>1134.4045</v>
+      </c>
+      <c r="M15">
+        <v>11800</v>
+      </c>
+      <c r="N15">
+        <v>8.25</v>
+      </c>
+      <c r="O15">
         <v>8.3</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>5287</v>
-      </c>
-      <c r="L15">
-        <v>44.0471</v>
-      </c>
-      <c r="M15">
-        <v>15500</v>
-      </c>
-      <c r="N15">
-        <v>8.3</v>
-      </c>
-      <c r="O15">
-        <v>8.35</v>
-      </c>
       <c r="P15">
-        <v>46600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="16">
@@ -784,7 +784,7 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>8.75</v>
+        <v>8.7</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="G16">
         <v>8.75</v>
@@ -808,22 +808,22 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>679204</v>
+        <v>1349939</v>
       </c>
       <c r="L16">
-        <v>5909.6748</v>
+        <v>11741.280050000001</v>
       </c>
       <c r="M16">
-        <v>363000</v>
+        <v>471000</v>
       </c>
       <c r="N16">
+        <v>8.65</v>
+      </c>
+      <c r="O16">
         <v>8.7</v>
       </c>
-      <c r="O16">
-        <v>8.75</v>
-      </c>
       <c r="P16">
-        <v>142700</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="17">
@@ -834,23 +834,23 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="F17">
         <v>0.31</v>
       </c>
       <c r="G17">
+        <v>0.33</v>
+      </c>
+      <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="H17">
-        <v>0.3</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -858,22 +858,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>23749200</v>
+        <v>30021266</v>
       </c>
       <c r="L17">
-        <v>7266.111</v>
+        <v>9602.16352</v>
       </c>
       <c r="M17">
-        <v>18040400</v>
+        <v>1499900</v>
       </c>
       <c r="N17">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="O17">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="P17">
-        <v>3810800</v>
+        <v>24240100</v>
       </c>
     </row>
     <row r="18">
@@ -884,46 +884,46 @@
         <v>-</v>
       </c>
       <c r="C18">
+        <v>2.14</v>
+      </c>
+      <c r="D18">
+        <v>-0.02</v>
+      </c>
+      <c r="E18">
+        <v>-0.9259259259259259</v>
+      </c>
+      <c r="F18">
+        <v>2.14</v>
+      </c>
+      <c r="G18">
+        <v>2.14</v>
+      </c>
+      <c r="H18">
+        <v>2.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>130010</v>
+      </c>
+      <c r="L18">
+        <v>276.30359999999996</v>
+      </c>
+      <c r="M18">
+        <v>4700</v>
+      </c>
+      <c r="N18">
+        <v>2.14</v>
+      </c>
+      <c r="O18">
         <v>2.16</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>2.18</v>
-      </c>
-      <c r="G18">
-        <v>2.18</v>
-      </c>
-      <c r="H18">
-        <v>2.16</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>77700</v>
-      </c>
-      <c r="L18">
-        <v>168.656</v>
-      </c>
-      <c r="M18">
-        <v>4500</v>
-      </c>
-      <c r="N18">
-        <v>2.16</v>
-      </c>
-      <c r="O18">
-        <v>2.18</v>
-      </c>
       <c r="P18">
-        <v>19700</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="19">
@@ -934,22 +934,22 @@
         <v>-</v>
       </c>
       <c r="C19">
+        <v>10.6</v>
+      </c>
+      <c r="D19">
+        <v>0.1</v>
+      </c>
+      <c r="E19">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="F19">
+        <v>10.5</v>
+      </c>
+      <c r="G19">
         <v>10.8</v>
       </c>
-      <c r="D19">
-        <v>-0.2</v>
-      </c>
-      <c r="E19">
-        <v>-1.8181818181818181</v>
-      </c>
-      <c r="F19">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>11</v>
-      </c>
       <c r="H19">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>125007</v>
+        <v>318799</v>
       </c>
       <c r="L19">
-        <v>1362.5656000000001</v>
+        <v>3357.3995</v>
       </c>
       <c r="M19">
-        <v>46200</v>
+        <v>29400</v>
       </c>
       <c r="N19">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="O19">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="P19">
-        <v>25600</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="20">
@@ -984,46 +984,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>0.2958579881656805</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="F20">
         <v>337</v>
       </c>
       <c r="G20">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H20">
+        <v>336</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>2304687</v>
+      </c>
+      <c r="L20">
+        <v>778502.554</v>
+      </c>
+      <c r="M20">
+        <v>487000</v>
+      </c>
+      <c r="N20">
         <v>337</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>1875224</v>
-      </c>
-      <c r="L20">
-        <v>634175.786</v>
-      </c>
-      <c r="M20">
-        <v>111400</v>
-      </c>
-      <c r="N20">
+      <c r="O20">
         <v>338</v>
       </c>
-      <c r="O20">
-        <v>339</v>
-      </c>
       <c r="P20">
-        <v>98600</v>
+        <v>211800</v>
       </c>
     </row>
     <row r="21">
@@ -1034,22 +1034,22 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="D21">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E21">
-        <v>-0.31347962382445144</v>
+        <v>-0.6309148264984227</v>
       </c>
       <c r="F21">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="G21">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="H21">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>173063</v>
+        <v>417258</v>
       </c>
       <c r="L21">
-        <v>27487.9135</v>
+        <v>65712.735</v>
       </c>
       <c r="M21">
-        <v>500</v>
+        <v>14800</v>
       </c>
       <c r="N21">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O21">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="P21">
-        <v>1600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="22">
@@ -1084,46 +1084,46 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="F22">
         <v>5.15</v>
       </c>
       <c r="G22">
+        <v>5.2</v>
+      </c>
+      <c r="H22">
+        <v>5.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>77205</v>
+      </c>
+      <c r="L22">
+        <v>397.09075</v>
+      </c>
+      <c r="M22">
+        <v>4500</v>
+      </c>
+      <c r="N22">
         <v>5.15</v>
       </c>
-      <c r="H22">
-        <v>5.05</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>47500</v>
-      </c>
-      <c r="L22">
-        <v>242.84</v>
-      </c>
-      <c r="M22">
-        <v>16100</v>
-      </c>
-      <c r="N22">
-        <v>5.05</v>
-      </c>
       <c r="O22">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P22">
-        <v>8700</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="23">
@@ -1134,22 +1134,22 @@
         <v>-</v>
       </c>
       <c r="C23">
+        <v>5.35</v>
+      </c>
+      <c r="D23">
+        <v>0.05</v>
+      </c>
+      <c r="E23">
+        <v>0.9433962264150944</v>
+      </c>
+      <c r="F23">
         <v>5.3</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>5.35</v>
       </c>
       <c r="G23">
         <v>5.35</v>
       </c>
       <c r="H23">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1158,22 +1158,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>106528</v>
+        <v>149400</v>
       </c>
       <c r="L23">
-        <v>559.3073</v>
+        <v>794.34</v>
       </c>
       <c r="M23">
-        <v>32100</v>
+        <v>3000</v>
       </c>
       <c r="N23">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="O23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P23">
-        <v>43300</v>
+        <v>39300</v>
       </c>
     </row>
     <row r="24">
@@ -1184,19 +1184,19 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="D24">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.9523809523809523</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G24">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H24">
         <v>2.08</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>164200</v>
+        <v>109800</v>
       </c>
       <c r="L24">
-        <v>341.536</v>
+        <v>230.602</v>
       </c>
       <c r="M24">
-        <v>98400</v>
+        <v>187000</v>
       </c>
       <c r="N24">
         <v>2.08</v>
       </c>
       <c r="O24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="P24">
-        <v>76000</v>
+        <v>159100</v>
       </c>
     </row>
     <row r="25">
@@ -1234,23 +1234,23 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="D25">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1.694915254237288</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="G25">
+        <v>18.5</v>
+      </c>
+      <c r="H25">
         <v>18.2</v>
       </c>
-      <c r="H25">
-        <v>17.7</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
@@ -1258,22 +1258,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4474887</v>
+        <v>6759324</v>
       </c>
       <c r="L25">
-        <v>80421.125</v>
+        <v>123685.3796</v>
       </c>
       <c r="M25">
-        <v>846800</v>
+        <v>96000</v>
       </c>
       <c r="N25">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="O25">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="P25">
-        <v>323200</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="26">
@@ -1284,22 +1284,22 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>34.5</v>
+        <v>34.25</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>-1.4388489208633093</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="H26">
-        <v>33.75</v>
+        <v>34.25</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>216028</v>
+        <v>308244</v>
       </c>
       <c r="L26">
-        <v>7386.74775</v>
+        <v>10609.06925</v>
       </c>
       <c r="M26">
-        <v>11000</v>
+        <v>21600</v>
       </c>
       <c r="N26">
         <v>34.25</v>
@@ -1323,7 +1323,7 @@
         <v>34.5</v>
       </c>
       <c r="P26">
-        <v>24200</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="27">
@@ -1334,46 +1334,46 @@
         <v>-</v>
       </c>
       <c r="C27">
+        <v>1.82</v>
+      </c>
+      <c r="D27">
+        <v>-0.02</v>
+      </c>
+      <c r="E27">
+        <v>-1.0869565217391304</v>
+      </c>
+      <c r="F27">
         <v>1.84</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1.85</v>
-      </c>
       <c r="G27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H27">
+        <v>1.82</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>8860867</v>
+      </c>
+      <c r="L27">
+        <v>16172.160240000001</v>
+      </c>
+      <c r="M27">
+        <v>1316800</v>
+      </c>
+      <c r="N27">
+        <v>1.82</v>
+      </c>
+      <c r="O27">
         <v>1.83</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>2120114</v>
-      </c>
-      <c r="L27">
-        <v>3904.23944</v>
-      </c>
-      <c r="M27">
-        <v>810000</v>
-      </c>
-      <c r="N27">
-        <v>1.84</v>
-      </c>
-      <c r="O27">
-        <v>1.85</v>
-      </c>
       <c r="P27">
-        <v>1211000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="28">
@@ -1384,22 +1384,22 @@
         <v>-</v>
       </c>
       <c r="C28">
+        <v>1.54</v>
+      </c>
+      <c r="D28">
+        <v>-0.01</v>
+      </c>
+      <c r="E28">
+        <v>-0.6451612903225806</v>
+      </c>
+      <c r="F28">
         <v>1.56</v>
-      </c>
-      <c r="D28">
-        <v>0.01</v>
-      </c>
-      <c r="E28">
-        <v>0.6451612903225806</v>
-      </c>
-      <c r="F28">
-        <v>1.55</v>
       </c>
       <c r="G28">
         <v>1.57</v>
       </c>
       <c r="H28">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1408,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>234500</v>
+        <v>624689</v>
       </c>
       <c r="L28">
-        <v>362.837</v>
+        <v>966.04075</v>
       </c>
       <c r="M28">
-        <v>85900</v>
+        <v>52300</v>
       </c>
       <c r="N28">
+        <v>1.54</v>
+      </c>
+      <c r="O28">
         <v>1.55</v>
       </c>
-      <c r="O28">
-        <v>1.56</v>
-      </c>
       <c r="P28">
-        <v>67400</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="29">
@@ -1437,19 +1437,19 @@
         <v>5.55</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>-0.8928571428571429</v>
       </c>
       <c r="F29">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G29">
         <v>5.6</v>
       </c>
       <c r="H29">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,13 +1458,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>356500</v>
+        <v>746211</v>
       </c>
       <c r="L29">
-        <v>1968.645</v>
+        <v>4115.07705</v>
       </c>
       <c r="M29">
-        <v>226000</v>
+        <v>700</v>
       </c>
       <c r="N29">
         <v>5.5</v>
@@ -1473,7 +1473,7 @@
         <v>5.55</v>
       </c>
       <c r="P29">
-        <v>38200</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="30">
@@ -1487,19 +1487,19 @@
         <v>1.86</v>
       </c>
       <c r="D30">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0.5405405405405406</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G30">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H30">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>159499</v>
+        <v>1267811</v>
       </c>
       <c r="L30">
-        <v>296.80214</v>
+        <v>2382.20179</v>
       </c>
       <c r="M30">
-        <v>28500</v>
+        <v>73500</v>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O30">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="P30">
-        <v>10300</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (6).xlsx
+++ b/Excel/StockQuotation (6).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:30:28</v>
+        <v>08/02/23 20:06:19</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>9223.52</v>
+        <v>9209.35</v>
       </c>
       <c r="B7" t="str">
-        <v>11.67 (0.1266%)</v>
+        <v>-14.17 (-0.1536%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>9241.96</v>
+        <v>9265.46</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>9197.46</v>
+        <v>9187.39</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>103442462</v>
+        <v>63276667</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>1067576195.09</v>
+        <v>952076379.65</v>
       </c>
     </row>
     <row r="9">
@@ -537,19 +537,19 @@
         <v>0.45</v>
       </c>
       <c r="D11">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>7.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="G11">
         <v>0.46</v>
       </c>
       <c r="H11">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -558,13 +558,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>33085588</v>
+        <v>12840683</v>
       </c>
       <c r="L11">
-        <v>14771.11967</v>
+        <v>5776.363240000001</v>
       </c>
       <c r="M11">
-        <v>500500</v>
+        <v>107200</v>
       </c>
       <c r="N11">
         <v>0.45</v>
@@ -573,7 +573,7 @@
         <v>0.46</v>
       </c>
       <c r="P11">
-        <v>2836700</v>
+        <v>2897600</v>
       </c>
     </row>
     <row r="12">
@@ -584,19 +584,19 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>-0.970873786407767</v>
       </c>
       <c r="F12">
         <v>2.06</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
         <v>2.04</v>
@@ -608,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1119925</v>
+        <v>895561</v>
       </c>
       <c r="L12">
-        <v>2299.92356</v>
+        <v>1827.65518</v>
       </c>
       <c r="M12">
-        <v>1005000</v>
+        <v>601700</v>
       </c>
       <c r="N12">
         <v>2.04</v>
@@ -623,7 +623,7 @@
         <v>2.06</v>
       </c>
       <c r="P12">
-        <v>200400</v>
+        <v>264000</v>
       </c>
     </row>
     <row r="13">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G13">
         <v>2.86</v>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5323644</v>
+        <v>3430492</v>
       </c>
       <c r="L13">
-        <v>15143.35806</v>
+        <v>9749.30854</v>
       </c>
       <c r="M13">
-        <v>304700</v>
+        <v>678100</v>
       </c>
       <c r="N13">
         <v>2.84</v>
@@ -673,7 +673,7 @@
         <v>2.86</v>
       </c>
       <c r="P13">
-        <v>1063800</v>
+        <v>1917900</v>
       </c>
     </row>
     <row r="14">
@@ -684,13 +684,13 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="D14">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E14">
-        <v>2.3255813953488373</v>
+        <v>-2.272727272727273</v>
       </c>
       <c r="F14">
         <v>0.44</v>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>10327040</v>
+        <v>5866400</v>
       </c>
       <c r="L14">
-        <v>4537.1922</v>
+        <v>2580.358</v>
       </c>
       <c r="M14">
-        <v>457500</v>
+        <v>2595800</v>
       </c>
       <c r="N14">
+        <v>0.43</v>
+      </c>
+      <c r="O14">
         <v>0.44</v>
       </c>
-      <c r="O14">
-        <v>0.45</v>
-      </c>
       <c r="P14">
-        <v>1798100</v>
+        <v>537900</v>
       </c>
     </row>
     <row r="15">
@@ -734,13 +734,13 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D15">
         <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F15">
         <v>8.25</v>
@@ -749,31 +749,31 @@
         <v>8.3</v>
       </c>
       <c r="H15">
+        <v>8.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>62782</v>
+      </c>
+      <c r="L15">
+        <v>518.53745</v>
+      </c>
+      <c r="M15">
+        <v>45000</v>
+      </c>
+      <c r="N15">
+        <v>8.2</v>
+      </c>
+      <c r="O15">
         <v>8.25</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>137355</v>
-      </c>
-      <c r="L15">
-        <v>1134.4045</v>
-      </c>
-      <c r="M15">
-        <v>11800</v>
-      </c>
-      <c r="N15">
-        <v>8.25</v>
-      </c>
-      <c r="O15">
-        <v>8.3</v>
-      </c>
       <c r="P15">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -784,46 +784,46 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>8.7</v>
+        <v>8.65</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-0.5747126436781609</v>
       </c>
       <c r="F16">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="G16">
         <v>8.75</v>
       </c>
       <c r="H16">
+        <v>8.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>2501441</v>
+      </c>
+      <c r="L16">
+        <v>21591.43955</v>
+      </c>
+      <c r="M16">
+        <v>33600</v>
+      </c>
+      <c r="N16">
+        <v>8.6</v>
+      </c>
+      <c r="O16">
         <v>8.65</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>1349939</v>
-      </c>
-      <c r="L16">
-        <v>11741.280050000001</v>
-      </c>
-      <c r="M16">
-        <v>471000</v>
-      </c>
-      <c r="N16">
-        <v>8.65</v>
-      </c>
-      <c r="O16">
-        <v>8.7</v>
-      </c>
       <c r="P16">
-        <v>124800</v>
+        <v>106600</v>
       </c>
     </row>
     <row r="17">
@@ -837,13 +837,13 @@
         <v>0.32</v>
       </c>
       <c r="D17">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>3.225806451612903</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="G17">
         <v>0.33</v>
@@ -858,22 +858,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>30021266</v>
+        <v>9943871</v>
       </c>
       <c r="L17">
-        <v>9602.16352</v>
+        <v>3185.6838399999997</v>
       </c>
       <c r="M17">
-        <v>1499900</v>
+        <v>12096000</v>
       </c>
       <c r="N17">
+        <v>0.31</v>
+      </c>
+      <c r="O17">
         <v>0.32</v>
       </c>
-      <c r="O17">
-        <v>0.33</v>
-      </c>
       <c r="P17">
-        <v>24240100</v>
+        <v>625400</v>
       </c>
     </row>
     <row r="18">
@@ -884,13 +884,13 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="D18">
         <v>-0.02</v>
       </c>
       <c r="E18">
-        <v>-0.9259259259259259</v>
+        <v>-0.9345794392523364</v>
       </c>
       <c r="F18">
         <v>2.14</v>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>130010</v>
+        <v>73100</v>
       </c>
       <c r="L18">
-        <v>276.30359999999996</v>
+        <v>155.568</v>
       </c>
       <c r="M18">
-        <v>4700</v>
+        <v>33300</v>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="P18">
-        <v>11800</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="19">
@@ -934,22 +934,22 @@
         <v>-</v>
       </c>
       <c r="C19">
+        <v>10.5</v>
+      </c>
+      <c r="D19">
+        <v>-0.1</v>
+      </c>
+      <c r="E19">
+        <v>-0.9433962264150944</v>
+      </c>
+      <c r="F19">
         <v>10.6</v>
       </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
-      <c r="E19">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="F19">
-        <v>10.5</v>
-      </c>
       <c r="G19">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H19">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>318799</v>
+        <v>233901</v>
       </c>
       <c r="L19">
-        <v>3357.3995</v>
+        <v>2468.6406</v>
       </c>
       <c r="M19">
-        <v>29400</v>
+        <v>400</v>
       </c>
       <c r="N19">
         <v>10.5</v>
@@ -973,7 +973,7 @@
         <v>10.6</v>
       </c>
       <c r="P19">
-        <v>28600</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="20">
@@ -987,43 +987,43 @@
         <v>338</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="F20">
+        <v>338</v>
+      </c>
+      <c r="G20">
+        <v>340</v>
+      </c>
+      <c r="H20">
         <v>337</v>
       </c>
-      <c r="G20">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>2114967</v>
+      </c>
+      <c r="L20">
+        <v>716071.182</v>
+      </c>
+      <c r="M20">
+        <v>34700</v>
+      </c>
+      <c r="N20">
+        <v>338</v>
+      </c>
+      <c r="O20">
         <v>339</v>
       </c>
-      <c r="H20">
-        <v>336</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>2304687</v>
-      </c>
-      <c r="L20">
-        <v>778502.554</v>
-      </c>
-      <c r="M20">
-        <v>487000</v>
-      </c>
-      <c r="N20">
-        <v>337</v>
-      </c>
-      <c r="O20">
-        <v>338</v>
-      </c>
       <c r="P20">
-        <v>211800</v>
+        <v>286100</v>
       </c>
     </row>
     <row r="21">
@@ -1034,46 +1034,46 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>157.5</v>
+        <v>156.5</v>
       </c>
       <c r="D21">
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>-0.6309148264984227</v>
+        <v>-0.6349206349206349</v>
       </c>
       <c r="F21">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="G21">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="H21">
+        <v>156</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>372042</v>
+      </c>
+      <c r="L21">
+        <v>58281.191</v>
+      </c>
+      <c r="M21">
+        <v>6000</v>
+      </c>
+      <c r="N21">
+        <v>156.5</v>
+      </c>
+      <c r="O21">
         <v>157</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>417258</v>
-      </c>
-      <c r="L21">
-        <v>65712.735</v>
-      </c>
-      <c r="M21">
-        <v>14800</v>
-      </c>
-      <c r="N21">
-        <v>157</v>
-      </c>
-      <c r="O21">
-        <v>157.5</v>
-      </c>
       <c r="P21">
-        <v>62400</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="22">
@@ -1084,46 +1084,46 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="D22">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E22">
-        <v>0.970873786407767</v>
+        <v>-0.9615384615384616</v>
       </c>
       <c r="F22">
+        <v>5.1</v>
+      </c>
+      <c r="G22">
         <v>5.15</v>
       </c>
-      <c r="G22">
-        <v>5.2</v>
-      </c>
       <c r="H22">
+        <v>5.05</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>68590</v>
+      </c>
+      <c r="L22">
+        <v>349.8635</v>
+      </c>
+      <c r="M22">
+        <v>10000</v>
+      </c>
+      <c r="N22">
         <v>5.1</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>77205</v>
-      </c>
-      <c r="L22">
-        <v>397.09075</v>
-      </c>
-      <c r="M22">
-        <v>4500</v>
-      </c>
-      <c r="N22">
+      <c r="O22">
         <v>5.15</v>
       </c>
-      <c r="O22">
-        <v>5.2</v>
-      </c>
       <c r="P22">
-        <v>40800</v>
+        <v>21400</v>
       </c>
     </row>
     <row r="23">
@@ -1134,46 +1134,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="D23">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E23">
-        <v>0.9433962264150944</v>
+        <v>-0.9345794392523364</v>
       </c>
       <c r="F23">
+        <v>5.4</v>
+      </c>
+      <c r="G23">
+        <v>5.4</v>
+      </c>
+      <c r="H23">
+        <v>5.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>672401</v>
+      </c>
+      <c r="L23">
+        <v>3544.2252999999996</v>
+      </c>
+      <c r="M23">
+        <v>106500</v>
+      </c>
+      <c r="N23">
+        <v>5.2</v>
+      </c>
+      <c r="O23">
         <v>5.3</v>
       </c>
-      <c r="G23">
-        <v>5.35</v>
-      </c>
-      <c r="H23">
-        <v>5.25</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>149400</v>
-      </c>
-      <c r="L23">
-        <v>794.34</v>
-      </c>
-      <c r="M23">
-        <v>3000</v>
-      </c>
-      <c r="N23">
-        <v>5.35</v>
-      </c>
-      <c r="O23">
-        <v>5.4</v>
-      </c>
       <c r="P23">
-        <v>39300</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="24">
@@ -1184,16 +1184,16 @@
         <v>-</v>
       </c>
       <c r="C24">
+        <v>2.1</v>
+      </c>
+      <c r="D24">
+        <v>-0.02</v>
+      </c>
+      <c r="E24">
+        <v>-0.9433962264150944</v>
+      </c>
+      <c r="F24">
         <v>2.12</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>2.1</v>
       </c>
       <c r="G24">
         <v>2.12</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>109800</v>
+        <v>635000</v>
       </c>
       <c r="L24">
-        <v>230.602</v>
+        <v>1330.308</v>
       </c>
       <c r="M24">
-        <v>187000</v>
+        <v>37300</v>
       </c>
       <c r="N24">
         <v>2.08</v>
       </c>
       <c r="O24">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P24">
-        <v>159100</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="25">
@@ -1234,22 +1234,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>-1.092896174863388</v>
       </c>
       <c r="F25">
         <v>18.3</v>
       </c>
       <c r="G25">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="H25">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1258,22 +1258,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>6759324</v>
+        <v>4232498</v>
       </c>
       <c r="L25">
-        <v>123685.3796</v>
+        <v>76604.99840000001</v>
       </c>
       <c r="M25">
-        <v>96000</v>
+        <v>436000</v>
       </c>
       <c r="N25">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="O25">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P25">
-        <v>252800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="26">
@@ -1287,43 +1287,43 @@
         <v>34.25</v>
       </c>
       <c r="D26">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>-1.4388489208633093</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>34.75</v>
+        <v>34.5</v>
       </c>
       <c r="G26">
-        <v>34.75</v>
+        <v>34.5</v>
       </c>
       <c r="H26">
+        <v>34</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>236361</v>
+      </c>
+      <c r="L26">
+        <v>8094.6095</v>
+      </c>
+      <c r="M26">
+        <v>314200</v>
+      </c>
+      <c r="N26">
+        <v>34</v>
+      </c>
+      <c r="O26">
         <v>34.25</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>308244</v>
-      </c>
-      <c r="L26">
-        <v>10609.06925</v>
-      </c>
-      <c r="M26">
-        <v>21600</v>
-      </c>
-      <c r="N26">
-        <v>34.25</v>
-      </c>
-      <c r="O26">
-        <v>34.5</v>
-      </c>
       <c r="P26">
-        <v>10800</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="27">
@@ -1334,46 +1334,46 @@
         <v>-</v>
       </c>
       <c r="C27">
+        <v>1.84</v>
+      </c>
+      <c r="D27">
+        <v>0.02</v>
+      </c>
+      <c r="E27">
+        <v>1.098901098901099</v>
+      </c>
+      <c r="F27">
         <v>1.82</v>
       </c>
-      <c r="D27">
-        <v>-0.02</v>
-      </c>
-      <c r="E27">
-        <v>-1.0869565217391304</v>
-      </c>
-      <c r="F27">
+      <c r="G27">
+        <v>1.85</v>
+      </c>
+      <c r="H27">
+        <v>1.81</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>13538520</v>
+      </c>
+      <c r="L27">
+        <v>24811.78485</v>
+      </c>
+      <c r="M27">
+        <v>640100</v>
+      </c>
+      <c r="N27">
+        <v>1.83</v>
+      </c>
+      <c r="O27">
         <v>1.84</v>
       </c>
-      <c r="G27">
-        <v>1.84</v>
-      </c>
-      <c r="H27">
-        <v>1.82</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>8860867</v>
-      </c>
-      <c r="L27">
-        <v>16172.160240000001</v>
-      </c>
-      <c r="M27">
-        <v>1316800</v>
-      </c>
-      <c r="N27">
-        <v>1.82</v>
-      </c>
-      <c r="O27">
-        <v>1.83</v>
-      </c>
       <c r="P27">
-        <v>6000</v>
+        <v>1137700</v>
       </c>
     </row>
     <row r="28">
@@ -1384,19 +1384,19 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="D28">
         <v>-0.01</v>
       </c>
       <c r="E28">
-        <v>-0.6451612903225806</v>
+        <v>-0.6493506493506493</v>
       </c>
       <c r="F28">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G28">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H28">
         <v>1.53</v>
@@ -1408,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>624689</v>
+        <v>3600215</v>
       </c>
       <c r="L28">
-        <v>966.04075</v>
+        <v>5663.373</v>
       </c>
       <c r="M28">
-        <v>52300</v>
+        <v>185100</v>
       </c>
       <c r="N28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
         <v>1.55</v>
       </c>
       <c r="P28">
-        <v>80600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
@@ -1434,22 +1434,22 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>5.35</v>
+      </c>
+      <c r="D29">
+        <v>-0.2</v>
+      </c>
+      <c r="E29">
+        <v>-3.6036036036036037</v>
+      </c>
+      <c r="F29">
         <v>5.55</v>
       </c>
-      <c r="D29">
-        <v>-0.05</v>
-      </c>
-      <c r="E29">
-        <v>-0.8928571428571429</v>
-      </c>
-      <c r="F29">
-        <v>5.6</v>
-      </c>
       <c r="G29">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="H29">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>746211</v>
+        <v>1626542</v>
       </c>
       <c r="L29">
-        <v>4115.07705</v>
+        <v>8852.3157</v>
       </c>
       <c r="M29">
-        <v>700</v>
+        <v>130700</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O29">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="P29">
-        <v>79200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="30">
@@ -1484,19 +1484,19 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.5376344086021505</v>
       </c>
       <c r="F30">
         <v>1.86</v>
       </c>
       <c r="G30">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H30">
         <v>1.86</v>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1267811</v>
+        <v>331300</v>
       </c>
       <c r="L30">
-        <v>2382.20179</v>
+        <v>618.974</v>
       </c>
       <c r="M30">
-        <v>73500</v>
+        <v>131100</v>
       </c>
       <c r="N30">
         <v>1.86</v>
@@ -1523,7 +1523,7 @@
         <v>1.87</v>
       </c>
       <c r="P30">
-        <v>200</v>
+        <v>83500</v>
       </c>
     </row>
   </sheetData>
